--- a/examples/SmallDrugCombo_Zhou_CellChemBio_2026/raw_data/9545combo_Manifest.xlsx
+++ b/examples/SmallDrugCombo_Zhou_CellChemBio_2026/raw_data/9545combo_Manifest.xlsx
@@ -47,13 +47,13 @@
     <t>CLID</t>
   </si>
   <si>
-    <t>CL131438</t>
+    <t>CL00100</t>
   </si>
   <si>
-    <t>CL130742</t>
+    <t>CL00103</t>
   </si>
   <si>
-    <t>CL131891</t>
+    <t>CL00101</t>
   </si>
   <si>
     <t>Evero_9545 combo_Treatment.xlsx</t>
@@ -62,7 +62,7 @@
     <t>0077_9545 combo_Treatment.xlsx</t>
   </si>
   <si>
-    <t>CL129757</t>
+    <t>CL00102</t>
   </si>
   <si>
     <t>Untreated.xlsx</t>
